--- a/public/project-manager-dashboard/AGUA_HIELO.xlsx
+++ b/public/project-manager-dashboard/AGUA_HIELO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LGress\Desktop\sicapsystem\public\project-manager-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E164114-8566-4F41-8951-2B0657CFBB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A426CCD-57EB-47C2-B6F1-3DCD64A20E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{62DA2B6E-C063-479F-B145-311EF53CCDE8}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="13845" xr2:uid="{62DA2B6E-C063-479F-B145-311EF53CCDE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
     <t>TOTAL ACUMULADO</t>
   </si>
   <si>
-    <t>CONSUMIBLES EN SITIO</t>
-  </si>
-  <si>
     <t>TOTAL:</t>
   </si>
   <si>
@@ -72,7 +69,10 @@
     <t>GASTOS GENERAL DE AGUA EMBOTELLADA Y HIELO</t>
   </si>
   <si>
-    <t>GASTOS DE  AGUA EMBOTELLADA</t>
+    <t>GASTOS DE CONSUMO AGUA EMBOTELLADA</t>
+  </si>
+  <si>
+    <t>AGUA EMBOTELLADA Y HIELO</t>
   </si>
 </sst>
 </file>
@@ -290,28 +290,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -320,13 +308,25 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -662,30 +662,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="F4" s="26" t="s">
+      <c r="A4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="F4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
     </row>
     <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -703,11 +703,11 @@
       <c r="F5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="27"/>
       <c r="J5" s="5" t="s">
         <v>4</v>
       </c>
@@ -721,60 +721,60 @@
       <c r="F6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="19"/>
+      <c r="G6" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="23"/>
+      <c r="I6" s="24"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7" s="8"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="G10" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="16" t="s">
+      <c r="G10" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16" t="s">
+      <c r="K10" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="L10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="23" t="s">
+      <c r="M10" s="18" t="s">
         <v>10</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="16"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="18"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F12" s="3">
         <v>1</v>
       </c>
       <c r="G12" s="9"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
       <c r="J12" s="10"/>
       <c r="K12" s="9"/>
       <c r="L12" s="13"/>
@@ -782,12 +782,18 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="L13" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M13" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="H10:I11"/>
+    <mergeCell ref="G10:G11"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="F4:J4"/>
     <mergeCell ref="F2:J2"/>
@@ -796,12 +802,6 @@
     <mergeCell ref="K10:K11"/>
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="H10:I11"/>
-    <mergeCell ref="G10:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
